--- a/ink statistic/ink statistic.xlsx
+++ b/ink statistic/ink statistic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\ink statistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44403F43-1C18-41D3-9388-A8B9AE141CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED7B57C-CD7B-4198-BA0A-D58A9CF8D9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <sheet name="Лист6" sheetId="13" r:id="rId10"/>
     <sheet name="спрос" sheetId="12" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2596,11 +2596,11 @@
         <v>24000</v>
       </c>
       <c r="G4" s="5">
-        <f>ROUNDUP(B4*F4/1000,0)</f>
+        <f t="shared" ref="G4:G18" si="0">ROUNDUP(B4*F4/1000,0)</f>
         <v>3</v>
       </c>
       <c r="H4" s="5">
-        <f t="shared" ref="H4:H12" si="0">ROUNDUP(E4/G4,1)</f>
+        <f t="shared" ref="H4:H12" si="1">ROUNDUP(E4/G4,1)</f>
         <v>5.6999999999999993</v>
       </c>
       <c r="I4" s="5">
@@ -2628,7 +2628,7 @@
         <v>16</v>
       </c>
       <c r="E5" s="1">
-        <f>SUM(C5:D5)</f>
+        <f t="shared" ref="E5:E18" si="2">SUM(C5:D5)</f>
         <v>16</v>
       </c>
       <c r="F5" s="5">
@@ -2636,18 +2636,18 @@
         <v>24000</v>
       </c>
       <c r="G5" s="5">
-        <f>ROUNDUP(B5*F5/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.3999999999999995</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <f t="shared" ref="J5:J12" si="1">G5*I5</f>
+        <f t="shared" ref="J5:J12" si="3">G5*I5</f>
         <v>0</v>
       </c>
       <c r="K5" s="5"/>
@@ -2668,7 +2668,7 @@
         <v>28</v>
       </c>
       <c r="E6" s="1">
-        <f>SUM(C6:D6)</f>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="F6" s="5">
@@ -2676,18 +2676,18 @@
         <v>24000</v>
       </c>
       <c r="G6" s="5">
-        <f>ROUNDUP(B6*F6/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="H6" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.6</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K6" s="5"/>
@@ -2708,7 +2708,7 @@
         <v>36</v>
       </c>
       <c r="E7" s="1">
-        <f>SUM(C7:D7)</f>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="F7" s="5">
@@ -2716,18 +2716,18 @@
         <v>24000</v>
       </c>
       <c r="G7" s="5">
-        <f>ROUNDUP(B7*F7/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="H7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
       </c>
       <c r="J7" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K7" s="5"/>
@@ -2757,7 +2757,7 @@
         <v>220</v>
       </c>
       <c r="E8" s="1">
-        <f>SUM(C8:D8)</f>
+        <f t="shared" si="2"/>
         <v>220</v>
       </c>
       <c r="F8" s="5">
@@ -2765,28 +2765,28 @@
         <v>24000</v>
       </c>
       <c r="G8" s="5">
-        <f>ROUNDUP(B8*F8/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="H8" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
       <c r="I8" s="5">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" si="1"/>
-        <v>189</v>
+        <f t="shared" si="3"/>
+        <v>157.5</v>
       </c>
       <c r="K8" s="5">
         <f>SUM(J4:J8)</f>
-        <v>189</v>
+        <v>157.5</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
         <f>K8*22+K8*3.2*90+950*90</f>
-        <v>144090</v>
+        <v>134325</v>
       </c>
       <c r="O8">
         <f>950+J9*5</f>
@@ -2807,7 +2807,7 @@
         <v>470</v>
       </c>
       <c r="E9" s="1">
-        <f>SUM(C9:D9)</f>
+        <f t="shared" si="2"/>
         <v>470</v>
       </c>
       <c r="F9" s="5">
@@ -2815,18 +2815,18 @@
         <v>24000</v>
       </c>
       <c r="G9" s="5">
-        <f>ROUNDUP(B9*F9/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>96</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.8999999999999995</v>
       </c>
       <c r="I9" s="5">
         <v>1</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>96</v>
       </c>
       <c r="K9" s="5"/>
@@ -2861,7 +2861,7 @@
         <v>86</v>
       </c>
       <c r="E10" s="1">
-        <f>SUM(C10:D10)</f>
+        <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="F10" s="5">
@@ -2869,25 +2869,25 @@
         <v>24000</v>
       </c>
       <c r="G10" s="5">
-        <f>ROUNDUP(B10*F10/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="H10" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.6</v>
       </c>
       <c r="I10" s="5">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J10" s="5">
-        <f t="shared" si="1"/>
-        <v>72</v>
+        <f t="shared" si="3"/>
+        <v>57.599999999999994</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5">
         <f>J10*3800+J10*22</f>
-        <v>275184</v>
+        <v>220147.19999999998</v>
       </c>
       <c r="P10" s="5">
         <v>192</v>
@@ -2919,7 +2919,7 @@
         <v>18</v>
       </c>
       <c r="E11" s="1">
-        <f>SUM(C11:D11)</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="F11" s="5">
@@ -2927,18 +2927,18 @@
         <v>24000</v>
       </c>
       <c r="G11" s="5">
-        <f>ROUNDUP(B11*F11/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="H11" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="I11" s="5">
         <v>3</v>
       </c>
       <c r="J11" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="K11" s="5"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="1">
-        <f>SUM(C12:D12)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F12" s="5">
@@ -2965,18 +2965,18 @@
         <v>24000</v>
       </c>
       <c r="G12" s="5">
-        <f>ROUNDUP(B12*F12/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="H12" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I12" s="5">
         <v>2</v>
       </c>
       <c r="J12" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="K12" s="5"/>
@@ -2991,12 +2991,12 @@
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="1">
-        <f>SUM(C13:D13)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5">
-        <f>ROUNDUP(B13*F13/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H13" s="5"/>
@@ -3014,12 +3014,12 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="1">
-        <f>SUM(C14:D14)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5">
-        <f>ROUNDUP(B14*F14/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H14" s="5"/>
@@ -3037,12 +3037,12 @@
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="1">
-        <f>SUM(C15:D15)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5">
-        <f>ROUNDUP(B15*F15/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H15" s="5"/>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="1">
-        <f>SUM(C16:D16)</f>
+        <f t="shared" si="2"/>
         <v>25000</v>
       </c>
       <c r="F16" s="5">
@@ -3073,11 +3073,11 @@
         <v>24000</v>
       </c>
       <c r="G16" s="5">
-        <f>ROUNDUP(B16*F16/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>18000</v>
       </c>
       <c r="H16" s="5">
-        <f t="shared" ref="H16:H17" si="2">ROUNDUP(E16/G16,1)</f>
+        <f t="shared" ref="H16:H17" si="4">ROUNDUP(E16/G16,1)</f>
         <v>1.4000000000000001</v>
       </c>
       <c r="I16" s="5"/>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="1">
-        <f>SUM(C17:D17)</f>
+        <f t="shared" si="2"/>
         <v>50000</v>
       </c>
       <c r="F17" s="5">
@@ -3107,11 +3107,11 @@
         <v>24000</v>
       </c>
       <c r="G17" s="5">
-        <f>ROUNDUP(B17*F17/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>6000</v>
       </c>
       <c r="H17" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.4</v>
       </c>
       <c r="I17" s="5"/>
@@ -3134,7 +3134,7 @@
         <v>240</v>
       </c>
       <c r="E18" s="1">
-        <f>SUM(C18:D18)</f>
+        <f t="shared" si="2"/>
         <v>850</v>
       </c>
       <c r="F18" s="5">
@@ -3142,7 +3142,7 @@
         <v>24000</v>
       </c>
       <c r="G18" s="5">
-        <f>ROUNDUP(B18*F18/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>429</v>
       </c>
       <c r="H18" s="5">
@@ -3160,7 +3160,7 @@
       <c r="L18" s="5"/>
       <c r="M18" s="16">
         <f>SUM(M8:M10)</f>
-        <v>449034</v>
+        <v>384232.19999999995</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">

--- a/ink statistic/ink statistic.xlsx
+++ b/ink statistic/ink statistic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\ink statistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED7B57C-CD7B-4198-BA0A-D58A9CF8D9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044EFB85-6999-4D13-BCB0-D94D5B581169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <sheet name="Лист6" sheetId="13" r:id="rId10"/>
     <sheet name="спрос" sheetId="12" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2776,7 +2776,7 @@
         <v>2.5</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" si="3"/>
+        <f>G8*I8</f>
         <v>157.5</v>
       </c>
       <c r="K8" s="5">
@@ -2785,8 +2785,8 @@
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
-        <f>K8*22+K8*3.2*90+950*90</f>
-        <v>134325</v>
+        <f>K8*5.6*90+K8*3.2*90</f>
+        <v>124740</v>
       </c>
       <c r="O8">
         <f>950+J9*5</f>
@@ -3160,7 +3160,7 @@
       <c r="L18" s="5"/>
       <c r="M18" s="16">
         <f>SUM(M8:M10)</f>
-        <v>384232.19999999995</v>
+        <v>374647.19999999995</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
